--- a/Results_experiment/exp_1/eval_cycle_XI.xlsx
+++ b/Results_experiment/exp_1/eval_cycle_XI.xlsx
@@ -447,13 +447,13 @@
         <v>534</v>
       </c>
       <c r="D2">
-        <v>-17.71102875366276</v>
+        <v>0.337241259362358</v>
       </c>
       <c r="E2">
-        <v>40.25948585010853</v>
+        <v>7.576997137748352</v>
       </c>
       <c r="F2">
-        <v>32.5588308347717</v>
+        <v>5.703125122850865</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -467,13 +467,13 @@
         <v>521</v>
       </c>
       <c r="D3">
-        <v>-39.82163599147894</v>
+        <v>0.5407948307535065</v>
       </c>
       <c r="E3">
-        <v>45.34351960310541</v>
+        <v>4.809206314337127</v>
       </c>
       <c r="F3">
-        <v>28.47700882585801</v>
+        <v>3.105419446705285</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -487,13 +487,13 @@
         <v>429</v>
       </c>
       <c r="D4">
-        <v>-37.78818894985906</v>
+        <v>0.5385425493020797</v>
       </c>
       <c r="E4">
-        <v>64.0617720416729</v>
+        <v>6.987390702952394</v>
       </c>
       <c r="F4">
-        <v>52.411746013102</v>
+        <v>4.707385571756007</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -507,13 +507,13 @@
         <v>374</v>
       </c>
       <c r="D5">
-        <v>-22.63252725222324</v>
+        <v>0.6076781889609244</v>
       </c>
       <c r="E5">
-        <v>29.17934193522542</v>
+        <v>3.759599959377991</v>
       </c>
       <c r="F5">
-        <v>19.66319454999212</v>
+        <v>2.91512970965017</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -527,13 +527,13 @@
         <v>251</v>
       </c>
       <c r="D6">
-        <v>-19.07953873839539</v>
+        <v>0.4663452731955368</v>
       </c>
       <c r="E6">
-        <v>28.9844526418916</v>
+        <v>4.725180657777133</v>
       </c>
       <c r="F6">
-        <v>19.81858533977037</v>
+        <v>3.529415464614967</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -547,13 +547,13 @@
         <v>237</v>
       </c>
       <c r="D7">
-        <v>-69.57583201125296</v>
+        <v>0.2685456543511253</v>
       </c>
       <c r="E7">
-        <v>53.6750483440181</v>
+        <v>5.464344266922428</v>
       </c>
       <c r="F7">
-        <v>38.83648135330732</v>
+        <v>4.490109451932494</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -567,13 +567,13 @@
         <v>223</v>
       </c>
       <c r="D8">
-        <v>-3.308947055465643</v>
+        <v>0.567459662130686</v>
       </c>
       <c r="E8">
-        <v>11.55662868608557</v>
+        <v>3.661498733627678</v>
       </c>
       <c r="F8">
-        <v>9.237277179789382</v>
+        <v>2.765923983279632</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -587,13 +587,13 @@
         <v>84</v>
       </c>
       <c r="D9">
-        <v>-26.04285661841611</v>
+        <v>0.1643387144912595</v>
       </c>
       <c r="E9">
-        <v>77.72061733835358</v>
+        <v>13.66234035138958</v>
       </c>
       <c r="F9">
-        <v>56.12879637841667</v>
+        <v>7.758253071634543</v>
       </c>
     </row>
   </sheetData>
